--- a/sample_data/radon_20250116.xlsx
+++ b/sample_data/radon_20250116.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://univie365-my.sharepoint.com/personal/steyrld69_univie_ac_at/Documents/T1 IML/scripts/sample_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://univie365-my.sharepoint.com/personal/steyrld69_univie_ac_at/Documents/oosi/sample_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{33358ABA-B5CB-4C11-AE90-FA18D6E46FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DAD9B62-F0E4-4706-9175-B82BCD1E424D}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="13_ncr:1_{33358ABA-B5CB-4C11-AE90-FA18D6E46FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{375FC1F6-E946-4D0F-B85C-F2812522E759}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_nan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
